--- a/order_forms/047_custom_heat_transfer_patch_order_form--order_forms.xlsx
+++ b/order_forms/047_custom_heat_transfer_patch_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1194,8 +1194,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option 1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option 2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option 3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option 1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option 2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option 3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'option 4'}</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'usd'}</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'USD'}</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'eur'}</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'EUR'}</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'gbp'}</t>
+          <t>gbp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'GBP'}</t>
+          <t>GBP</t>
         </is>
       </c>
     </row>
